--- a/VerveStacks_BRA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C373377D-008B-4790-A503-6FF290D4C597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B01110-6A8B-46BF-AD55-C7997C7B6F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{939C4651-4F69-4543-8304-3F04EB5DD0DE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1F4B768F-DE2D-46C0-BF84-E78307434D0D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26C255F-643A-42F9-A2BF-E89876CE12E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3089907E-7A81-4DC4-B2E2-4F42D59C27F5}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
